--- a/data/May.xlsx
+++ b/data/May.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0B1902-7C43-4BF7-AC75-399ECC429BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,34 +15,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Author</author>
+    <author>ผู้สร้าง</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
-          <t xml:space="preserve">This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
+          <t>This is a reach-based metric. Reach-based metrics are de-duplicated metrics so you might see different numbers based on the level at which you are viewing data.</t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
         <r>
           <rPr>
+            <sz val="12"/>
             <rFont val="Arial"/>
-            <color/>
-            <sz val="12"/>
           </rPr>
           <t xml:space="preserve">     </t>
         </r>
@@ -52,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="161">
   <si>
     <t>Ad name</t>
   </si>
@@ -258,9 +256,6 @@
     <t>หมดกองนี้ ลูกค้ารับไปเลย 23,XXX บาท</t>
   </si>
   <si>
-    <t>Total of 97 results</t>
-  </si>
-  <si>
     <t>Primary status</t>
   </si>
   <si>
@@ -484,9 +479,6 @@
   </si>
   <si>
     <t>1999.76</t>
-  </si>
-  <si>
-    <t>27758.59</t>
   </si>
   <si>
     <t>Reach</t>
@@ -546,8 +538,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -555,17 +547,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -603,136 +597,140 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<theme xmlns="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <themeElements>
-    <clrScheme name="Office">
-      <dk1>
-        <sysClr val="windowText" lastClr="000000"/>
-      </dk1>
-      <lt1>
-        <sysClr val="window" lastClr="FFFFFF"/>
-      </lt1>
-      <dk2>
-        <srgbClr val="44546A"/>
-      </dk2>
-      <lt2>
-        <srgbClr val="E7E6E6"/>
-      </lt2>
-      <accent1>
-        <srgbClr val="5B9BD5"/>
-      </accent1>
-      <accent2>
-        <srgbClr val="ED7D31"/>
-      </accent2>
-      <accent3>
-        <srgbClr val="A5A5A5"/>
-      </accent3>
-      <accent4>
-        <srgbClr val="FFC000"/>
-      </accent4>
-      <accent5>
-        <srgbClr val="4472C4"/>
-      </accent5>
-      <accent6>
-        <srgbClr val="70AD47"/>
-      </accent6>
-      <hlink>
-        <srgbClr val="0563C1"/>
-      </hlink>
-      <folHlink>
-        <srgbClr val="954F72"/>
-      </folHlink>
-    </clrScheme>
-    <fontScheme name="Office">
-      <majorFont>
-        <latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック Light"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线 Light"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Times New Roman"/>
-        <font script="Hebr" typeface="Times New Roman"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="MoolBoran"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Times New Roman"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </majorFont>
-      <minorFont>
-        <latin typeface="Calibri" panose="020F0502020204030204"/>
-        <ea typeface=""/>
-        <cs typeface=""/>
-        <font script="Jpan" typeface="游ゴシック"/>
-        <font script="Hang" typeface="맑은 고딕"/>
-        <font script="Hans" typeface="等线"/>
-        <font script="Hant" typeface="新細明體"/>
-        <font script="Arab" typeface="Arial"/>
-        <font script="Hebr" typeface="Arial"/>
-        <font script="Thai" typeface="Tahoma"/>
-        <font script="Ethi" typeface="Nyala"/>
-        <font script="Beng" typeface="Vrinda"/>
-        <font script="Gujr" typeface="Shruti"/>
-        <font script="Khmr" typeface="DaunPenh"/>
-        <font script="Knda" typeface="Tunga"/>
-        <font script="Guru" typeface="Raavi"/>
-        <font script="Cans" typeface="Euphemia"/>
-        <font script="Cher" typeface="Plantagenet Cherokee"/>
-        <font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <font script="Tibt" typeface="Microsoft Himalaya"/>
-        <font script="Thaa" typeface="MV Boli"/>
-        <font script="Deva" typeface="Mangal"/>
-        <font script="Telu" typeface="Gautami"/>
-        <font script="Taml" typeface="Latha"/>
-        <font script="Syrc" typeface="Estrangelo Edessa"/>
-        <font script="Orya" typeface="Kalinga"/>
-        <font script="Mlym" typeface="Kartika"/>
-        <font script="Laoo" typeface="DokChampa"/>
-        <font script="Sinh" typeface="Iskoola Pota"/>
-        <font script="Mong" typeface="Mongolian Baiti"/>
-        <font script="Viet" typeface="Arial"/>
-        <font script="Uigh" typeface="Microsoft Uighur"/>
-        <font script="Geor" typeface="Sylfaen"/>
-      </minorFont>
-    </fontScheme>
-    <fmtScheme name="Office">
-      <fillStyleLst>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -788,8 +786,8 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </fillStyleLst>
-      <lnStyleLst>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -811,8 +809,8 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-      </lnStyleLst>
-      <effectStyleLst>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst/>
         </a:effectStyle>
@@ -828,8 +826,8 @@
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
-      </effectStyleLst>
-      <bgFillStyleLst>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -866,96 +864,96 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-      </bgFillStyleLst>
-    </fmtScheme>
-  </themeElements>
-  <objectDefaults/>
-  <extraClrSchemeLst/>
-</theme>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -991,33 +989,33 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -1053,33 +1051,33 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -1115,33 +1113,33 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -1177,33 +1175,33 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -1239,33 +1237,33 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -1301,33 +1299,33 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -1363,33 +1361,33 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1425,33 +1423,33 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -1487,33 +1485,33 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -1549,33 +1547,33 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -1611,33 +1609,33 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -1673,33 +1671,33 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1735,33 +1733,33 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -1797,33 +1795,33 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1859,33 +1857,33 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -1921,33 +1919,33 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1983,33 +1981,33 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" s="2">
         <v>0</v>
@@ -2045,33 +2043,33 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
@@ -2107,33 +2105,33 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -2169,33 +2167,33 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
@@ -2231,33 +2229,33 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -2293,33 +2291,33 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
@@ -2355,33 +2353,33 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -2417,33 +2415,33 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -2479,33 +2477,33 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
@@ -2541,33 +2539,33 @@
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -2603,33 +2601,33 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
@@ -2665,33 +2663,33 @@
         <v>0</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -2727,33 +2725,33 @@
         <v>0</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
@@ -2789,33 +2787,33 @@
         <v>0</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -2851,33 +2849,33 @@
         <v>0</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -2913,33 +2911,33 @@
         <v>0</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -2975,33 +2973,33 @@
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -3037,33 +3035,33 @@
         <v>0</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
@@ -3099,33 +3097,33 @@
         <v>0</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -3161,33 +3159,33 @@
         <v>0</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -3223,33 +3221,33 @@
         <v>0</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -3285,33 +3283,33 @@
         <v>0</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
@@ -3347,33 +3345,33 @@
         <v>0</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -3409,33 +3407,33 @@
         <v>0</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -3471,33 +3469,33 @@
         <v>0</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -3533,33 +3531,33 @@
         <v>0</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -3595,33 +3593,33 @@
         <v>0</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -3657,33 +3655,33 @@
         <v>0</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -3719,33 +3717,33 @@
         <v>0</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -3781,33 +3779,33 @@
         <v>0</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -3843,33 +3841,33 @@
         <v>0</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -3905,33 +3903,33 @@
         <v>0</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -3967,33 +3965,33 @@
         <v>0</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -4029,33 +4027,33 @@
         <v>0</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -4091,33 +4089,33 @@
         <v>0</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -4153,33 +4151,33 @@
         <v>0</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -4215,33 +4213,33 @@
         <v>0</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -4277,33 +4275,33 @@
         <v>0</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
@@ -4339,33 +4337,33 @@
         <v>0</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -4401,33 +4399,33 @@
         <v>0</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -4463,33 +4461,33 @@
         <v>0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F59" s="2">
         <v>1782</v>
@@ -4525,33 +4523,33 @@
         <v>27</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" s="2">
         <v>36779</v>
@@ -4587,33 +4585,33 @@
         <v>6</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" s="2">
         <v>1497</v>
@@ -4649,33 +4647,33 @@
         <v>36</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="2">
         <v>40657</v>
@@ -4711,33 +4709,33 @@
         <v>8</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F63" s="2">
         <v>1459</v>
@@ -4773,33 +4771,33 @@
         <v>28</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F64" s="2">
         <v>33171</v>
@@ -4835,33 +4833,33 @@
         <v>6</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F65" s="2">
         <v>183</v>
@@ -4897,33 +4895,33 @@
         <v>4</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F66" s="2">
         <v>2213</v>
@@ -4959,33 +4957,33 @@
         <v>25</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F67" s="2">
         <v>22</v>
@@ -5021,33 +5019,33 @@
         <v>0</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F68" s="2">
         <v>56751</v>
@@ -5083,33 +5081,33 @@
         <v>8</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F69" s="2">
         <v>955</v>
@@ -5145,33 +5143,33 @@
         <v>19</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F70" s="2">
         <v>433</v>
@@ -5207,33 +5205,33 @@
         <v>9</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F71" s="2">
         <v>42322</v>
@@ -5269,33 +5267,33 @@
         <v>9</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F72" s="2">
         <v>102</v>
@@ -5331,33 +5329,33 @@
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F73" s="2">
         <v>1601</v>
@@ -5393,33 +5391,33 @@
         <v>33</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F74" s="2">
         <v>42764</v>
@@ -5455,33 +5453,33 @@
         <v>8</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F75" s="2">
         <v>738</v>
@@ -5517,33 +5515,33 @@
         <v>3</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F76" s="2">
         <v>1268</v>
@@ -5579,33 +5577,33 @@
         <v>22</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F77" s="2">
         <v>42630</v>
@@ -5641,33 +5639,33 @@
         <v>11</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F78" s="2">
         <v>175</v>
@@ -5703,33 +5701,33 @@
         <v>0</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F79" s="2">
         <v>1252</v>
@@ -5765,33 +5763,33 @@
         <v>22</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F80" s="2">
         <v>25288</v>
@@ -5827,33 +5825,33 @@
         <v>10</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F81" s="2">
         <v>175</v>
@@ -5889,33 +5887,33 @@
         <v>1</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F82" s="2">
         <v>984</v>
@@ -5951,33 +5949,33 @@
         <v>22</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="2">
         <v>198</v>
@@ -6013,33 +6011,33 @@
         <v>0</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F84" s="2">
         <v>28290</v>
@@ -6075,33 +6073,33 @@
         <v>5</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F85" s="2">
         <v>787</v>
@@ -6137,33 +6135,33 @@
         <v>27</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F86" s="2">
         <v>251</v>
@@ -6199,33 +6197,33 @@
         <v>5</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F87" s="2">
         <v>47387</v>
@@ -6261,33 +6259,33 @@
         <v>14</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F88" s="2">
         <v>384</v>
@@ -6323,33 +6321,33 @@
         <v>1</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F89" s="2">
         <v>648</v>
@@ -6385,33 +6383,33 @@
         <v>9</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F90" s="2">
         <v>1124</v>
@@ -6447,33 +6445,33 @@
         <v>18</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F91" s="2">
         <v>41495</v>
@@ -6509,33 +6507,33 @@
         <v>8</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F92" s="2">
         <v>1195</v>
@@ -6571,33 +6569,33 @@
         <v>0</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F93" s="2">
         <v>1516</v>
@@ -6633,33 +6631,33 @@
         <v>42</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F94" s="2">
         <v>648</v>
@@ -6695,33 +6693,33 @@
         <v>21</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F95" s="2">
         <v>450</v>
@@ -6757,33 +6755,33 @@
         <v>8</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F96" s="2">
         <v>36752</v>
@@ -6819,33 +6817,33 @@
         <v>10</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F97" s="2">
         <v>718</v>
@@ -6881,33 +6879,33 @@
         <v>0</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F98" s="2">
         <v>53669</v>
@@ -6943,81 +6941,20 @@
         <v>15</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F99" s="2">
-        <v>360755</v>
-      </c>
-      <c r="G99" s="2">
-        <v>817604</v>
-      </c>
-      <c r="H99" s="2">
-        <v>811172</v>
-      </c>
-      <c r="I99" s="2">
-        <v>496434</v>
-      </c>
-      <c r="J99" s="2">
-        <v>213071</v>
-      </c>
-      <c r="K99" s="2">
-        <v>3517</v>
-      </c>
-      <c r="L99" s="2">
-        <v>127</v>
-      </c>
-      <c r="M99" s="2">
-        <v>58</v>
-      </c>
-      <c r="N99" s="2">
-        <v>2334</v>
-      </c>
-      <c r="O99" s="2">
-        <v>2037</v>
-      </c>
-      <c r="P99" s="2">
-        <v>500</v>
-      </c>
-      <c r="Q99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>